--- a/data/trans_orig/POLIPATOLOGIA_2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_2-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas en 2007</t>
+          <t>Población con dos o más enfermedades crónicas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>58877</t>
+          <t>59597</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>92095</t>
+          <t>91393</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53487</t>
+          <t>54152</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82314</t>
+          <t>82853</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>120107</t>
+          <t>120467</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>166110</t>
+          <t>163606</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>381681</t>
+          <t>382383</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>414899</t>
+          <t>414179</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>224366</t>
+          <t>223827</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>253193</t>
+          <t>252528</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>614347</t>
+          <t>616851</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>660350</t>
+          <t>659990</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,56%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41581</t>
+          <t>42625</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69464</t>
+          <t>69037</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76865</t>
+          <t>76692</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>110135</t>
+          <t>108642</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>127546</t>
+          <t>125936</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>169642</t>
+          <t>167925</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>297470</t>
+          <t>297897</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>325353</t>
+          <t>324309</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>261730</t>
+          <t>263223</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>295000</t>
+          <t>295173</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>569157</t>
+          <t>570874</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>611253</t>
+          <t>612863</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,95%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>105380</t>
+          <t>104482</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>143914</t>
+          <t>140765</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43297</t>
+          <t>44923</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66985</t>
+          <t>69682</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>154518</t>
+          <t>154938</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>200707</t>
+          <t>203128</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>398475</t>
+          <t>401624</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>437009</t>
+          <t>437907</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>100797</t>
+          <t>98100</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>124485</t>
+          <t>122859</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>509464</t>
+          <t>507043</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>555653</t>
+          <t>555233</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,18%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>284411</t>
+          <t>281881</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>344530</t>
+          <t>344089</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>183989</t>
+          <t>182434</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>229420</t>
+          <t>230214</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>480675</t>
+          <t>478306</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>558414</t>
+          <t>558179</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,59%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>893804</t>
+          <t>894245</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>953923</t>
+          <t>956453</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>484865</t>
+          <t>484071</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>530296</t>
+          <t>531851</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1394206</t>
+          <t>1394441</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1471945</t>
+          <t>1474314</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,5%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60443</t>
+          <t>60456</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92629</t>
+          <t>91097</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>170237</t>
+          <t>173212</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>217641</t>
+          <t>217133</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>242246</t>
+          <t>240308</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>298716</t>
+          <t>298469</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>257926</t>
+          <t>259458</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>290112</t>
+          <t>290099</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>351111</t>
+          <t>351619</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>398515</t>
+          <t>395540</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>620591</t>
+          <t>620838</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>677061</t>
+          <t>678999</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,86%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4860</t>
+          <t>4672</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16880</t>
+          <t>16986</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>480340</t>
+          <t>482251</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>550045</t>
+          <t>550960</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>490838</t>
+          <t>490782</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>564595</t>
+          <t>562559</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281321</t>
+          <t>281215</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>293341</t>
+          <t>293529</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>698715</t>
+          <t>697800</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>768420</t>
+          <t>766509</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>982365</t>
+          <t>984401</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1056122</t>
+          <t>1056178</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>603598</t>
+          <t>605615</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>690912</t>
+          <t>698734</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1082028</t>
+          <t>1083319</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1189370</t>
+          <t>1189185</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1706832</t>
+          <t>1710256</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1850191</t>
+          <t>1848918</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2579278</t>
+          <t>2571456</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2666592</t>
+          <t>2664575</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2188754</t>
+          <t>2188939</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2296096</t>
+          <t>2294805</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4798123</t>
+          <t>4799396</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4941482</t>
+          <t>4938058</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,28%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas en 2012</t>
+          <t>Población con dos o más enfermedades crónicas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69484</t>
+          <t>68271</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>105873</t>
+          <t>104898</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52055</t>
+          <t>54161</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83470</t>
+          <t>85567</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>130901</t>
+          <t>130559</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>177812</t>
+          <t>176620</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>331338</t>
+          <t>332313</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>367727</t>
+          <t>368940</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>230984</t>
+          <t>228887</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>262399</t>
+          <t>260293</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>573853</t>
+          <t>575045</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>620764</t>
+          <t>621106</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,63%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69034</t>
+          <t>69454</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>103841</t>
+          <t>104417</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>78000</t>
+          <t>77986</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>113255</t>
+          <t>112949</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>153963</t>
+          <t>153583</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>206948</t>
+          <t>204301</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,0%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>314956</t>
+          <t>314380</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>349763</t>
+          <t>349343</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>224756</t>
+          <t>225062</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>260011</t>
+          <t>260025</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>549860</t>
+          <t>552507</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>602845</t>
+          <t>603225</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,71%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>167082</t>
+          <t>168266</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>214984</t>
+          <t>215279</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80659</t>
+          <t>83029</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>114155</t>
+          <t>114007</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>260789</t>
+          <t>257818</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>322839</t>
+          <t>315799</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,5%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>414431</t>
+          <t>414136</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>462333</t>
+          <t>461149</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145974</t>
+          <t>146122</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>179470</t>
+          <t>177100</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>566705</t>
+          <t>573745</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>628755</t>
+          <t>631726</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>71,02%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>298536</t>
+          <t>298922</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>361874</t>
+          <t>364627</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>200903</t>
+          <t>198503</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>253082</t>
+          <t>250667</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>511513</t>
+          <t>510539</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>595647</t>
+          <t>595014</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,9%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>797135</t>
+          <t>794382</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>860473</t>
+          <t>860087</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>513575</t>
+          <t>515990</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>565754</t>
+          <t>568154</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1330020</t>
+          <t>1330653</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1414154</t>
+          <t>1415128</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,49%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>103342</t>
+          <t>104265</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>141718</t>
+          <t>144103</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>323317</t>
+          <t>326862</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>382086</t>
+          <t>380214</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>442371</t>
+          <t>441001</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>512036</t>
+          <t>512197</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,26%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>368878</t>
+          <t>366493</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>407254</t>
+          <t>406331</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>379436</t>
+          <t>381308</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>438205</t>
+          <t>434660</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>760082</t>
+          <t>759921</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>829747</t>
+          <t>831117</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,33%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9716</t>
+          <t>9589</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27044</t>
+          <t>27695</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>501085</t>
+          <t>502275</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>569268</t>
+          <t>569895</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>515900</t>
+          <t>516214</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>591827</t>
+          <t>593550</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,13%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>239838</t>
+          <t>239187</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>257166</t>
+          <t>257293</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>540083</t>
+          <t>539456</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>608266</t>
+          <t>607076</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>784406</t>
+          <t>782683</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>860333</t>
+          <t>860019</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,49%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>776359</t>
+          <t>783601</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>886195</t>
+          <t>887448</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1315902</t>
+          <t>1313223</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1432011</t>
+          <t>1430949</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2118267</t>
+          <t>2135664</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2278013</t>
+          <t>2286774</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,8%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2535715</t>
+          <t>2534462</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2645551</t>
+          <t>2638309</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2118114</t>
+          <t>2119176</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2234223</t>
+          <t>2236902</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4694022</t>
+          <t>4685261</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4853768</t>
+          <t>4836371</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,37%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas en 2016</t>
+          <t>Población con dos o más enfermedades crónicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>81588</t>
+          <t>82003</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>118439</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>70577</t>
+          <t>68945</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>102011</t>
+          <t>103164</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>161457</t>
+          <t>160945</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>212122</t>
+          <t>212788</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>312216</t>
+          <t>310653</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>347504</t>
+          <t>347089</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>245044</t>
+          <t>243891</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>276478</t>
+          <t>278110</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>564025</t>
+          <t>563359</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>614690</t>
+          <t>615202</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,26%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64883</t>
+          <t>65254</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>97637</t>
+          <t>97014</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66307</t>
+          <t>66885</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>101563</t>
+          <t>100054</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>139529</t>
+          <t>141068</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>184894</t>
+          <t>188368</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>279590</t>
+          <t>280213</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>312344</t>
+          <t>311973</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>270710</t>
+          <t>272219</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>305966</t>
+          <t>305388</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>564606</t>
+          <t>561132</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>609971</t>
+          <t>608432</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>122909</t>
+          <t>123017</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>162244</t>
+          <t>162748</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46597</t>
+          <t>47740</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72861</t>
+          <t>73333</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>178615</t>
+          <t>175490</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>228627</t>
+          <t>226448</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>359670</t>
+          <t>359166</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>399005</t>
+          <t>398897</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93262</t>
+          <t>92790</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>119526</t>
+          <t>118383</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>459409</t>
+          <t>461588</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>509421</t>
+          <t>512546</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,49%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>266276</t>
+          <t>265705</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>323802</t>
+          <t>324547</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>208191</t>
+          <t>209362</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>260155</t>
+          <t>262451</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>491473</t>
+          <t>488300</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>566869</t>
+          <t>568004</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>825836</t>
+          <t>825091</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>883362</t>
+          <t>883933</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>565721</t>
+          <t>563425</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>617685</t>
+          <t>616514</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1408645</t>
+          <t>1407510</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1484041</t>
+          <t>1487214</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,28%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>156766</t>
+          <t>158738</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>203568</t>
+          <t>203293</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>311086</t>
+          <t>311800</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>365701</t>
+          <t>366514</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>483692</t>
+          <t>481739</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>555528</t>
+          <t>556378</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,94%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>417138</t>
+          <t>417413</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>463940</t>
+          <t>461968</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>372543</t>
+          <t>371730</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>427158</t>
+          <t>426444</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>803422</t>
+          <t>802572</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>875258</t>
+          <t>877211</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>64,55%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8976</t>
+          <t>8968</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24001</t>
+          <t>24101</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>435352</t>
+          <t>431352</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>500988</t>
+          <t>500489</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>449255</t>
+          <t>449267</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>521575</t>
+          <t>522234</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,14%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>263144</t>
+          <t>263044</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>278169</t>
+          <t>278177</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>581037</t>
+          <t>581536</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>646673</t>
+          <t>650673</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>847595</t>
+          <t>846936</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>919915</t>
+          <t>919903</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>762324</t>
+          <t>762548</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>859668</t>
+          <t>861083</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1208376</t>
+          <t>1215031</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1332563</t>
+          <t>1334142</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2006201</t>
+          <t>2009861</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2158236</t>
+          <t>2162992</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2526054</t>
+          <t>2524639</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2623398</t>
+          <t>2623174</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2199033</t>
+          <t>2197454</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2323220</t>
+          <t>2316565</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4759082</t>
+          <t>4754326</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4911117</t>
+          <t>4907457</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,94%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas en 2023</t>
+          <t>Población con dos o más enfermedades crónicas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>132398</t>
+          <t>131771</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>172773</t>
+          <t>173753</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>158527</t>
+          <t>160183</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>194786</t>
+          <t>193261</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>300477</t>
+          <t>299639</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>356256</t>
+          <t>354174</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>332439</t>
+          <t>331459</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>372814</t>
+          <t>373441</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>252681</t>
+          <t>254206</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>288940</t>
+          <t>287284</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>596423</t>
+          <t>598505</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>652202</t>
+          <t>653040</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,55%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>131844</t>
+          <t>131232</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>171710</t>
+          <t>172571</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>138525</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>170885</t>
+          <t>170868</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>276970</t>
+          <t>277480</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>330217</t>
+          <t>331025</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,65%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>280503</t>
+          <t>279642</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>320369</t>
+          <t>320981</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>211695</t>
+          <t>211712</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>243650</t>
+          <t>244055</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>504576</t>
+          <t>503768</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>557823</t>
+          <t>557313</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,76%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56648</t>
+          <t>61498</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>256105</t>
+          <t>254550</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>83923</t>
+          <t>84529</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104814</t>
+          <t>104857</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>104784</t>
+          <t>116083</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>361677</t>
+          <t>360236</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,13%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>412159</t>
+          <t>413714</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>611616</t>
+          <t>606766</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62097</t>
+          <t>62054</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82988</t>
+          <t>82382</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>473498</t>
+          <t>474939</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>730391</t>
+          <t>719092</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>86,1%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>332513</t>
+          <t>331873</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>397878</t>
+          <t>395042</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>402579</t>
+          <t>400860</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>753723</t>
+          <t>709457</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>749805</t>
+          <t>751683</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1199568</t>
+          <t>1261502</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>62,67%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>636941</t>
+          <t>639777</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>702306</t>
+          <t>702946</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>224371</t>
+          <t>268637</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>575515</t>
+          <t>577234</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>813344</t>
+          <t>751410</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1263107</t>
+          <t>1261229</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,66%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>154594</t>
+          <t>152489</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>197950</t>
+          <t>198475</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>425895</t>
+          <t>426698</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>572059</t>
+          <t>563848</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>594655</t>
+          <t>595173</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>764823</t>
+          <t>769944</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>58,49%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>277096</t>
+          <t>276571</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>320452</t>
+          <t>322557</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>269276</t>
+          <t>277487</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>415440</t>
+          <t>414637</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>551558</t>
+          <t>546437</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>721726</t>
+          <t>721208</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,79%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21606</t>
+          <t>21627</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>59835</t>
+          <t>58532</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>331336</t>
+          <t>332390</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>382622</t>
+          <t>386919</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>364974</t>
+          <t>363637</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>430500</t>
+          <t>429317</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,85%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>180672</t>
+          <t>181975</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>218901</t>
+          <t>218880</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>378749</t>
+          <t>374452</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>430035</t>
+          <t>428981</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>571378</t>
+          <t>572561</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>636904</t>
+          <t>638241</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,7%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>793123</t>
+          <t>832080</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1134313</t>
+          <t>1130674</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1655880</t>
+          <t>1647383</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2186846</t>
+          <t>2101264</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2547971</t>
+          <t>2538441</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3215488</t>
+          <t>3171296</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2241747</t>
+          <t>2245386</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2582937</t>
+          <t>2543980</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1390912</t>
+          <t>1476494</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1921878</t>
+          <t>1930375</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3738330</t>
+          <t>3782522</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4405847</t>
+          <t>4415377</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,5%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/POLIPATOLOGIA_2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_2-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>59597</t>
+          <t>58812</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>91393</t>
+          <t>91541</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54152</t>
+          <t>55186</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82853</t>
+          <t>83449</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>120467</t>
+          <t>121969</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>163606</t>
+          <t>164426</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>382383</t>
+          <t>382235</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>414179</t>
+          <t>414964</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>223827</t>
+          <t>223231</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>252528</t>
+          <t>251494</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>616851</t>
+          <t>616031</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>659990</t>
+          <t>658488</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,37%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42625</t>
+          <t>42291</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69037</t>
+          <t>68746</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76692</t>
+          <t>75274</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108642</t>
+          <t>108173</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>125936</t>
+          <t>126090</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>167925</t>
+          <t>168092</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>297897</t>
+          <t>298188</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>324309</t>
+          <t>324643</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>263223</t>
+          <t>263692</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>295173</t>
+          <t>296591</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>570874</t>
+          <t>570707</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>612863</t>
+          <t>612709</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,93%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>104482</t>
+          <t>103047</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>140765</t>
+          <t>141303</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44923</t>
+          <t>44298</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69682</t>
+          <t>69815</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>154938</t>
+          <t>157514</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>203128</t>
+          <t>203173</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,61%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>401624</t>
+          <t>401086</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>437907</t>
+          <t>439342</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>98100</t>
+          <t>97967</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122859</t>
+          <t>123484</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>507043</t>
+          <t>506998</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>555233</t>
+          <t>552657</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>77,82%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>281881</t>
+          <t>282913</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>344089</t>
+          <t>344471</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>182434</t>
+          <t>181702</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>230214</t>
+          <t>228615</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>478306</t>
+          <t>482149</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>558179</t>
+          <t>559688</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>894245</t>
+          <t>893863</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>956453</t>
+          <t>955421</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>484071</t>
+          <t>485670</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>531851</t>
+          <t>532583</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1394441</t>
+          <t>1392932</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1474314</t>
+          <t>1470471</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,31%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60456</t>
+          <t>60336</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>91097</t>
+          <t>90465</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>173212</t>
+          <t>169842</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>217133</t>
+          <t>218587</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>240308</t>
+          <t>243326</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>298469</t>
+          <t>299592</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,59%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>259458</t>
+          <t>260090</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>290099</t>
+          <t>290219</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>351619</t>
+          <t>350165</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>395540</t>
+          <t>398910</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>620838</t>
+          <t>619715</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>678999</t>
+          <t>675981</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,53%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16986</t>
+          <t>16588</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>482251</t>
+          <t>483302</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>550960</t>
+          <t>548122</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>490782</t>
+          <t>488904</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>562559</t>
+          <t>559477</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,17%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281215</t>
+          <t>281613</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>293529</t>
+          <t>293518</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>697800</t>
+          <t>700638</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>766509</t>
+          <t>765458</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>984401</t>
+          <t>987483</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1056178</t>
+          <t>1058056</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,4%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>605615</t>
+          <t>604775</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>698734</t>
+          <t>693896</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1083319</t>
+          <t>1077523</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1189185</t>
+          <t>1194022</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1710256</t>
+          <t>1707119</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1848918</t>
+          <t>1848148</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2571456</t>
+          <t>2576294</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2664575</t>
+          <t>2665415</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2188939</t>
+          <t>2184102</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2294805</t>
+          <t>2300601</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4799396</t>
+          <t>4800166</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4938058</t>
+          <t>4941195</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,32%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68271</t>
+          <t>70798</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>104898</t>
+          <t>103939</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54161</t>
+          <t>53083</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>85567</t>
+          <t>84673</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>130559</t>
+          <t>132451</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>176620</t>
+          <t>178648</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>332313</t>
+          <t>333272</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>368940</t>
+          <t>366413</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>228887</t>
+          <t>229781</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>260293</t>
+          <t>261371</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>575045</t>
+          <t>573017</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>621106</t>
+          <t>619214</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,38%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69454</t>
+          <t>69022</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>104417</t>
+          <t>106825</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77986</t>
+          <t>77754</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>112949</t>
+          <t>112149</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>153583</t>
+          <t>154613</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>204301</t>
+          <t>202843</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>314380</t>
+          <t>311972</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>349343</t>
+          <t>349775</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>225062</t>
+          <t>225862</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>260025</t>
+          <t>260257</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>552507</t>
+          <t>553965</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>603225</t>
+          <t>602195</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,57%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>168266</t>
+          <t>168567</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>215279</t>
+          <t>217167</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>83029</t>
+          <t>82191</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>114007</t>
+          <t>114129</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>257818</t>
+          <t>261514</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>315799</t>
+          <t>316581</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,59%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>414136</t>
+          <t>412248</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>461149</t>
+          <t>460848</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146122</t>
+          <t>146000</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>177100</t>
+          <t>177938</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>573745</t>
+          <t>572963</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>631726</t>
+          <t>628030</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,6%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>298922</t>
+          <t>295628</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>364627</t>
+          <t>359300</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>198503</t>
+          <t>201216</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>250667</t>
+          <t>251977</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>510539</t>
+          <t>513780</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>595014</t>
+          <t>597049</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,0%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>794382</t>
+          <t>799709</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>860087</t>
+          <t>863381</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>515990</t>
+          <t>514680</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>568154</t>
+          <t>565441</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1330653</t>
+          <t>1328618</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1415128</t>
+          <t>1411887</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,32%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>104265</t>
+          <t>103132</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>144103</t>
+          <t>141972</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>326862</t>
+          <t>327011</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>380214</t>
+          <t>382836</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>441001</t>
+          <t>442976</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>512197</t>
+          <t>510404</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,12%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>366493</t>
+          <t>368624</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>406331</t>
+          <t>407464</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>381308</t>
+          <t>378686</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>434660</t>
+          <t>434511</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>759921</t>
+          <t>761714</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>831117</t>
+          <t>829142</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,18%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>8989</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27695</t>
+          <t>26462</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>502275</t>
+          <t>499804</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>569895</t>
+          <t>569168</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>516214</t>
+          <t>511950</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>593550</t>
+          <t>586236</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>42,6%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>239187</t>
+          <t>240420</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>257293</t>
+          <t>257893</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>539456</t>
+          <t>540183</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>607076</t>
+          <t>609547</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>782683</t>
+          <t>789997</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>860019</t>
+          <t>864283</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,8%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>783601</t>
+          <t>775312</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>887448</t>
+          <t>880411</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1313223</t>
+          <t>1314390</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1430949</t>
+          <t>1436130</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2135664</t>
+          <t>2132792</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2286774</t>
+          <t>2288986</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,83%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2534462</t>
+          <t>2541499</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2638309</t>
+          <t>2646598</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2119176</t>
+          <t>2113995</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2236902</t>
+          <t>2235735</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4685261</t>
+          <t>4683049</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4836371</t>
+          <t>4839243</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,41%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>82003</t>
+          <t>81067</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>118439</t>
+          <t>118256</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>68945</t>
+          <t>69343</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>103164</t>
+          <t>104835</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>160945</t>
+          <t>160445</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>212788</t>
+          <t>212675</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,4%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>310653</t>
+          <t>310836</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>347089</t>
+          <t>348025</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>243891</t>
+          <t>242220</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>278110</t>
+          <t>277712</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>563359</t>
+          <t>563472</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>615202</t>
+          <t>615702</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,33%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65254</t>
+          <t>63968</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>97014</t>
+          <t>96174</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66885</t>
+          <t>66493</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>100054</t>
+          <t>100758</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>141068</t>
+          <t>139636</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>188368</t>
+          <t>183068</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>280213</t>
+          <t>281053</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>311973</t>
+          <t>313259</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>272219</t>
+          <t>271515</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>305388</t>
+          <t>305780</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>561132</t>
+          <t>566432</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>608432</t>
+          <t>609864</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,37%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>123017</t>
+          <t>123420</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>162748</t>
+          <t>163297</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47740</t>
+          <t>47169</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73333</t>
+          <t>73218</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>175490</t>
+          <t>176125</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>226448</t>
+          <t>226882</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,98%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>359166</t>
+          <t>358617</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>398897</t>
+          <t>398494</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92790</t>
+          <t>92905</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>118383</t>
+          <t>118954</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>461588</t>
+          <t>461154</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>512546</t>
+          <t>511911</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,4%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>265705</t>
+          <t>263977</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>324547</t>
+          <t>322646</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>209362</t>
+          <t>209973</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>262451</t>
+          <t>261526</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>488300</t>
+          <t>489066</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>568004</t>
+          <t>568526</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>825091</t>
+          <t>826992</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>883933</t>
+          <t>885661</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>563425</t>
+          <t>564350</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>616514</t>
+          <t>615903</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1407510</t>
+          <t>1406988</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1487214</t>
+          <t>1486448</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,24%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>158738</t>
+          <t>158473</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>203293</t>
+          <t>204718</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>311800</t>
+          <t>313783</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>366514</t>
+          <t>370531</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>481739</t>
+          <t>484508</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>556378</t>
+          <t>554828</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,83%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>417413</t>
+          <t>415988</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>461968</t>
+          <t>462233</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>371730</t>
+          <t>367713</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>426444</t>
+          <t>424461</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>802572</t>
+          <t>804122</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>877211</t>
+          <t>874442</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,35%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8968</t>
+          <t>8912</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24101</t>
+          <t>23723</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>431352</t>
+          <t>434630</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>500489</t>
+          <t>505012</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>449267</t>
+          <t>450150</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>522234</t>
+          <t>525862</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,41%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>263044</t>
+          <t>263422</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>278177</t>
+          <t>278233</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>581536</t>
+          <t>577013</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>650673</t>
+          <t>647395</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>846936</t>
+          <t>843308</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>919903</t>
+          <t>919020</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,12%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>762548</t>
+          <t>757371</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>861083</t>
+          <t>856487</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1215031</t>
+          <t>1214229</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1334142</t>
+          <t>1332024</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2009861</t>
+          <t>2007095</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2162992</t>
+          <t>2167889</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,34%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2524639</t>
+          <t>2529235</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2623174</t>
+          <t>2628351</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2197454</t>
+          <t>2199572</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2316565</t>
+          <t>2317367</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4754326</t>
+          <t>4749429</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4907457</t>
+          <t>4910223</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>70,98%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>151259</t>
+          <t>168073</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>131771</t>
+          <t>148885</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>173753</t>
+          <t>189926</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>176777</t>
+          <t>194032</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>160183</t>
+          <t>175025</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>193261</t>
+          <t>211747</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>328036</t>
+          <t>362104</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>299639</t>
+          <t>333209</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>354174</t>
+          <t>390469</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,58%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>353953</t>
+          <t>382545</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>331459</t>
+          <t>360692</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>373441</t>
+          <t>401733</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>270690</t>
+          <t>294379</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>254206</t>
+          <t>276664</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287284</t>
+          <t>313386</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>624643</t>
+          <t>676925</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>598505</t>
+          <t>648560</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>653040</t>
+          <t>705820</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>67,93%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>151142</t>
+          <t>158700</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>131232</t>
+          <t>137770</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>172571</t>
+          <t>178900</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>153800</t>
+          <t>172828</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>138525</t>
+          <t>158255</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>170868</t>
+          <t>191151</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>304943</t>
+          <t>331527</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>277480</t>
+          <t>306584</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>331025</t>
+          <t>361791</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,92%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>301071</t>
+          <t>324512</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>279642</t>
+          <t>304312</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>320981</t>
+          <t>345442</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>228780</t>
+          <t>250315</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>211712</t>
+          <t>231992</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>244055</t>
+          <t>264888</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>529850</t>
+          <t>574828</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>503768</t>
+          <t>544564</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>557313</t>
+          <t>599771</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,17%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>155384</t>
+          <t>167344</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61498</t>
+          <t>146889</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>254550</t>
+          <t>189219</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>94626</t>
+          <t>103727</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>84529</t>
+          <t>92122</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104857</t>
+          <t>115479</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>250010</t>
+          <t>271071</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116083</t>
+          <t>246183</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>360236</t>
+          <t>295658</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>44,86%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>512880</t>
+          <t>304268</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>413714</t>
+          <t>282393</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>606766</t>
+          <t>324723</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>72285</t>
+          <t>83770</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62054</t>
+          <t>72018</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82382</t>
+          <t>95375</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>585165</t>
+          <t>388038</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>474939</t>
+          <t>363451</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>719092</t>
+          <t>412926</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>62,65%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>363056</t>
+          <t>392836</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>331873</t>
+          <t>360892</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>395042</t>
+          <t>428088</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>530277</t>
+          <t>366276</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>400860</t>
+          <t>341963</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>709457</t>
+          <t>392825</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>893333</t>
+          <t>759112</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>751683</t>
+          <t>719132</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1261502</t>
+          <t>795181</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>39,9%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>671763</t>
+          <t>739007</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>639777</t>
+          <t>703755</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>702946</t>
+          <t>770951</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>447817</t>
+          <t>494935</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>268637</t>
+          <t>468386</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>577234</t>
+          <t>519248</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1119579</t>
+          <t>1233942</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>751410</t>
+          <t>1197873</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1261229</t>
+          <t>1273922</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>63,92%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>174712</t>
+          <t>190486</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>152489</t>
+          <t>167496</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>198475</t>
+          <t>214277</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>480606</t>
+          <t>450918</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>426698</t>
+          <t>427103</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>563848</t>
+          <t>475416</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>655318</t>
+          <t>641403</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>595173</t>
+          <t>605356</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>769944</t>
+          <t>679490</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>48,58%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>300334</t>
+          <t>377478</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>276571</t>
+          <t>353687</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>322557</t>
+          <t>400468</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>360729</t>
+          <t>379932</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>277487</t>
+          <t>355434</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>414637</t>
+          <t>403747</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>661063</t>
+          <t>757411</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>546437</t>
+          <t>719324</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>721208</t>
+          <t>793458</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>56,72%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>36751</t>
+          <t>37695</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21627</t>
+          <t>22434</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58532</t>
+          <t>57397</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>358693</t>
+          <t>392527</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>332390</t>
+          <t>364392</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>386919</t>
+          <t>419381</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>395444</t>
+          <t>430222</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>363637</t>
+          <t>395161</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>429317</t>
+          <t>463703</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,88%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>203756</t>
+          <t>199533</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>181975</t>
+          <t>179831</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>218880</t>
+          <t>214794</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>402678</t>
+          <t>451754</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>374452</t>
+          <t>424900</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>428981</t>
+          <t>479889</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>606434</t>
+          <t>651287</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>572561</t>
+          <t>617806</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>638241</t>
+          <t>686348</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,46%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1032304</t>
+          <t>1115133</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>832080</t>
+          <t>1055474</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1130674</t>
+          <t>1170892</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1794779</t>
+          <t>1680307</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1647383</t>
+          <t>1626323</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2101264</t>
+          <t>1733392</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2827083</t>
+          <t>2795440</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2538441</t>
+          <t>2714086</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3171296</t>
+          <t>2873832</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>40,6%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2343756</t>
+          <t>2327343</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2245386</t>
+          <t>2271584</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2543980</t>
+          <t>2387002</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1782979</t>
+          <t>1955086</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1476494</t>
+          <t>1902001</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1930375</t>
+          <t>2009070</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>4126735</t>
+          <t>4282429</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3782522</t>
+          <t>4204037</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4415377</t>
+          <t>4363783</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>61,65%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
